--- a/invalidCodes/invalidCodes_existenciasOptex.xlsx.xlsx
+++ b/invalidCodes/invalidCodes_existenciasOptex.xlsx.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -479,31 +479,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,31 +515,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>50966</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>50981</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -611,19 +611,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>53639</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51144</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51622</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>51622</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -731,10 +731,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>52658</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>51733</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
